--- a/hrcheck/examples/mini_test2/本月花名册_修复报告.xlsx
+++ b/hrcheck/examples/mini_test2/本月花名册_修复报告.xlsx
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -601,7 +601,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-11 01:15:06</t>
+          <t>2026-06-11 01:23:33</t>
         </is>
       </c>
     </row>
